--- a/docs/qa/SECURITY_AUDIT_2026-09-03.xlsx
+++ b/docs/qa/SECURITY_AUDIT_2026-09-03.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pre-launch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Method" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Findings'!$A$5:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-launch'!$A$5:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1191,13 +1193,598 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pre-launch checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Everything that must be true before real users reach GAADIIQ. Ordered by when it is needed, not by size. Tick the Done column as you go — the Summary sheet counts what is left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Context: the app is in testing. The Vercel project name is deliberately obscure to keep it out of search results and casual discovery — that is intentional and is NOT a defect. See PL-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Where to do it</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PL-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Confirm ENVIRONMENT=production on the API service</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Five protections collapse together if this string is wrong, and all of them fail silently: the admin dependency hands an unauthenticated caller a synthetic Dev Admin; OTPs get logged in plaintext; auth cookies lose the Secure flag; /metrics skips its token check; payments accept without verification. (SEC-02)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Render dashboard → gaadiiq-api → Environment</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PL-02</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Turn on Vercel Deployment Protection</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>The single highest-value item for keeping people out during testing. Password or Vercel Authentication covers the whole web app including every preview. The project name keeps you out of search results; it does not stop anyone who has the URL.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Vercel → project → Settings → Deployment Protection</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="74" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Close public sign-ups, or require email confirmation</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Without this, anyone who reaches the app can create an account and use it. Obscurity does not gate registration.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Supabase → Authentication → Providers / Email</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="74" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PL-04</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>At rename</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Set ALLOWED_ORIGIN_REGEX anchored to the team slug</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>The current pattern matches the project-name PREFIX, which anyone can register on Vercel (gaaadiiq-anything.vercel.app matches). Anchor on the team slug at the END instead — that is the part an attacker cannot mint. No code change needed: the env var overrides config.py (verified). (SEC-03)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Render dashboard → gaadiiq-api → Environment</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Deferred deliberately: the regex would hardcode the current project name, which is about to change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="74" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>PL-05</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Before users</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Decide the API access story</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>The API is public and CORS does not gate it — CORS only stops browsers on other origins from reading responses; curl ignores it entirely. The APK also carries the production API URL compiled in, so anyone with a build reaches live data.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Cloudflare in front + TRUSTED_PROXY_SECRET / REQUIRE_TRUSTED_PROXY (already built, not switched on)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>docs/CLOUDFLARE.md. Turning the lock on before Cloudflare actually fronts the service refuses every request — a self-inflicted outage. Order matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="74" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PL-06</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Before users</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Confirm MARKETPLACE_ENABLED is off until KYC is ready</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Gates listings and KYC. Defaults to False in code; confirm the deployed value matches intent.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Render dashboard</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="74" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PL-07</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Before users</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Tell loan applicants what happens next</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>The lender hand-off is manual by design while payments are pending, and the admin queue is where applications land. If the screen implies a lender is processing it, people wait for a call on an automated timeline that does not exist.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>apps/gaadiiq-angular — loan application confirmation screen</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="74" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PL-08</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Add ng test to CI</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ci-web.yml runs Playwright but never the unit suite. That is how 13 broken specs sat on master unnoticed, including four guarding a price rule that was wrong on five screens.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci-web.yml</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2 hours</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="74" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PL-09</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Resolve the duplicate frontend declaration</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>render.yaml declares a gaadiiq-web static site while the live web app is on Vercel. Applying that blueprint stands up a second, stale copy on a different URL.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>render.yaml</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="74" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PL-10</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Generate the release keystore and set the four GitHub secrets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Without them the signed release bundle job stays skipped, so there is no Play Store build. The keystore must be generated by you and never committed.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Local machine + GitHub → Settings → Secrets</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>docs/ANDROID_RELEASE.md. Losing the keystore means never updating the app under the same listing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="74" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PL-11</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Apply migration 018 and reconcile the two schema homes</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Schema lives in 25 Alembic migrations AND hand-run schema_setup_batch*.sql files. Marketplace and loan tables exist only in the SQL files, so shipping code that needs them does not ship the tables.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Supabase SQL editor + apps/api/alembic</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PL-12</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Fix dark mode contrast failures</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>About twenty AA failures from hardcoded hexes that predate the theme tokens. e2e/contrast.spec.ts covers light theme only today.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>apps/gaadiiq-angular styles</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="74" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>PL-13</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Run a dependency vulnerability scan</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by the 3 Sep audit at all — no SCA was run against requirements.txt or package-lock.json.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>pip-audit / npm audit, or Dependabot</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="74" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PL-14</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Review Supabase row-level security policies</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>The database enforces its own rules outside this codebase, so the API audit says nothing about them. A permissive policy would bypass every check in FastAPI.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Supabase → Authentication → Policies</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:H19"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Now,Before users,At rename,Before launch"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1220,6 +1807,11 @@
           <t>By severity</t>
         </is>
       </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Pre-launch progress</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1231,6 +1823,15 @@
         <f>COUNTIF(Findings!$D$6:$D$15,A5)</f>
         <v/>
       </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Items total</t>
+        </is>
+      </c>
+      <c r="E5" s="15">
+        <f>COUNTA('Pre-launch'!$A$6:$A$19)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -1242,6 +1843,15 @@
         <f>COUNTIF(Findings!$D$6:$D$15,A6)</f>
         <v/>
       </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" s="15">
+        <f>COUNTIF('Pre-launch'!$G$6:$G$19,"Yes")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -1253,6 +1863,15 @@
         <f>COUNTIF(Findings!$D$6:$D$15,A7)</f>
         <v/>
       </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Not done</t>
+        </is>
+      </c>
+      <c r="E7" s="15">
+        <f>COUNTA('Pre-launch'!$A$6:$A$19)-COUNTIF('Pre-launch'!$G$6:$G$19,"Yes")-COUNTIF('Pre-launch'!$G$6:$G$19,"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -1262,6 +1881,15 @@
       </c>
       <c r="B8" s="15">
         <f>COUNTIF(Findings!$D$6:$D$15,A8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Blocking now</t>
+        </is>
+      </c>
+      <c r="E8" s="13">
+        <f>COUNTIFS('Pre-launch'!$B$6:$B$19,"Now",'Pre-launch'!$G$6:$G$19,"&lt;&gt;Yes")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +2043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/qa/SECURITY_AUDIT_2026-09-03.xlsx
+++ b/docs/qa/SECURITY_AUDIT_2026-09-03.xlsx
@@ -720,14 +720,14 @@
           <t>Five protections all hang on ENVIRONMENT == 'production' being exactly right</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Your call</t>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Verified OK</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>render.yaml sets it as a managed value, so it should be correct — but verify rather than assume. Strict mode reasons from the database host (a heuristic); a wrong heuristic takes the service down.</t>
+          <t>Confirmed on the Render dashboard 3 Sep 2026: ENVIRONMENT = production. All six dependent protections are live — admin bypass closed, OTP logging raises, cookies Secure, /metrics token enforced, payments verify, rate limiter ENABLED. STRICT_ENVIRONMENT_CHECK still unset, so a future mismatch would warn rather than refuse to boot; that remains a judgement call, not a gap.</t>
         </is>
       </c>
     </row>
@@ -1300,8 +1300,16 @@
           <t>5 min</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Verified on the Render dashboard 3 Sep 2026 — screenshot confirms ENVIRONMENT = production on gaadiiq-api.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="74" customHeight="1">
       <c r="A7" s="4" t="inlineStr">

--- a/docs/qa/SECURITY_AUDIT_2026-09-03.xlsx
+++ b/docs/qa/SECURITY_AUDIT_2026-09-03.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pre-launch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Method" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Findings'!$A$5:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-launch'!$A$5:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -718,14 +720,14 @@
           <t>Five protections all hang on ENVIRONMENT == 'production' being exactly right</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Your call</t>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Verified OK</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -750,7 +752,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>render.yaml sets it as a managed value, so it should be correct — but verify rather than assume. Strict mode reasons from the database host (a heuristic); a wrong heuristic takes the service down.</t>
+          <t>Confirmed on the Render dashboard 3 Sep 2026: ENVIRONMENT = production. All six dependent protections are live — admin bypass closed, OTP logging raises, cookies Secure, /metrics token enforced, payments verify, rate limiter ENABLED. STRICT_ENVIRONMENT_CHECK still unset, so a future mismatch would warn rather than refuse to boot; that remains a judgement call, not a gap.</t>
         </is>
       </c>
     </row>
@@ -1191,13 +1193,606 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pre-launch checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Everything that must be true before real users reach GAADIIQ. Ordered by when it is needed, not by size. Tick the Done column as you go — the Summary sheet counts what is left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Context: the app is in testing. The Vercel project name is deliberately obscure to keep it out of search results and casual discovery — that is intentional and is NOT a defect. See PL-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Where to do it</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PL-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Confirm ENVIRONMENT=production on the API service</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Five protections collapse together if this string is wrong, and all of them fail silently: the admin dependency hands an unauthenticated caller a synthetic Dev Admin; OTPs get logged in plaintext; auth cookies lose the Secure flag; /metrics skips its token check; payments accept without verification. (SEC-02)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Render dashboard → gaadiiq-api → Environment</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Verified on the Render dashboard 3 Sep 2026 — screenshot confirms ENVIRONMENT = production on gaadiiq-api.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PL-02</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Turn on Vercel Deployment Protection</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>The single highest-value item for keeping people out during testing. Password or Vercel Authentication covers the whole web app including every preview. The project name keeps you out of search results; it does not stop anyone who has the URL.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Vercel → project → Settings → Deployment Protection</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="74" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Close public sign-ups, or require email confirmation</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Without this, anyone who reaches the app can create an account and use it. Obscurity does not gate registration.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Supabase → Authentication → Providers / Email</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="74" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PL-04</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>At rename</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Set ALLOWED_ORIGIN_REGEX anchored to the team slug</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>The current pattern matches the project-name PREFIX, which anyone can register on Vercel (gaaadiiq-anything.vercel.app matches). Anchor on the team slug at the END instead — that is the part an attacker cannot mint. No code change needed: the env var overrides config.py (verified). (SEC-03)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Render dashboard → gaadiiq-api → Environment</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Deferred deliberately: the regex would hardcode the current project name, which is about to change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="74" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>PL-05</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Before users</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Decide the API access story</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>The API is public and CORS does not gate it — CORS only stops browsers on other origins from reading responses; curl ignores it entirely. The APK also carries the production API URL compiled in, so anyone with a build reaches live data.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Cloudflare in front + TRUSTED_PROXY_SECRET / REQUIRE_TRUSTED_PROXY (already built, not switched on)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>docs/CLOUDFLARE.md. Turning the lock on before Cloudflare actually fronts the service refuses every request — a self-inflicted outage. Order matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="74" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PL-06</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Before users</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Confirm MARKETPLACE_ENABLED is off until KYC is ready</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Gates listings and KYC. Defaults to False in code; confirm the deployed value matches intent.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Render dashboard</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="74" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PL-07</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Before users</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Tell loan applicants what happens next</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>The lender hand-off is manual by design while payments are pending, and the admin queue is where applications land. If the screen implies a lender is processing it, people wait for a call on an automated timeline that does not exist.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>apps/gaadiiq-angular — loan application confirmation screen</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="74" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PL-08</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Add ng test to CI</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ci-web.yml runs Playwright but never the unit suite. That is how 13 broken specs sat on master unnoticed, including four guarding a price rule that was wrong on five screens.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci-web.yml</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2 hours</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="74" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PL-09</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Resolve the duplicate frontend declaration</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>render.yaml declares a gaadiiq-web static site while the live web app is on Vercel. Applying that blueprint stands up a second, stale copy on a different URL.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>render.yaml</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="74" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PL-10</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Generate the release keystore and set the four GitHub secrets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Without them the signed release bundle job stays skipped, so there is no Play Store build. The keystore must be generated by you and never committed.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Local machine + GitHub → Settings → Secrets</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>docs/ANDROID_RELEASE.md. Losing the keystore means never updating the app under the same listing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="74" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PL-11</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Apply migration 018 and reconcile the two schema homes</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Schema lives in 25 Alembic migrations AND hand-run schema_setup_batch*.sql files. Marketplace and loan tables exist only in the SQL files, so shipping code that needs them does not ship the tables.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Supabase SQL editor + apps/api/alembic</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PL-12</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Fix dark mode contrast failures</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>About twenty AA failures from hardcoded hexes that predate the theme tokens. e2e/contrast.spec.ts covers light theme only today.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>apps/gaadiiq-angular styles</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="74" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>PL-13</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Run a dependency vulnerability scan</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by the 3 Sep audit at all — no SCA was run against requirements.txt or package-lock.json.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>pip-audit / npm audit, or Dependabot</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="74" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PL-14</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Review Supabase row-level security policies</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>The database enforces its own rules outside this codebase, so the API audit says nothing about them. A permissive policy would bypass every check in FastAPI.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Supabase → Authentication → Policies</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:H19"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Now,Before users,At rename,Before launch"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1220,6 +1815,11 @@
           <t>By severity</t>
         </is>
       </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Pre-launch progress</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1231,6 +1831,15 @@
         <f>COUNTIF(Findings!$D$6:$D$15,A5)</f>
         <v/>
       </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Items total</t>
+        </is>
+      </c>
+      <c r="E5" s="15">
+        <f>COUNTA('Pre-launch'!$A$6:$A$19)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -1242,6 +1851,15 @@
         <f>COUNTIF(Findings!$D$6:$D$15,A6)</f>
         <v/>
       </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" s="15">
+        <f>COUNTIF('Pre-launch'!$G$6:$G$19,"Yes")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -1253,6 +1871,15 @@
         <f>COUNTIF(Findings!$D$6:$D$15,A7)</f>
         <v/>
       </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Not done</t>
+        </is>
+      </c>
+      <c r="E7" s="15">
+        <f>COUNTA('Pre-launch'!$A$6:$A$19)-COUNTIF('Pre-launch'!$G$6:$G$19,"Yes")-COUNTIF('Pre-launch'!$G$6:$G$19,"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -1262,6 +1889,15 @@
       </c>
       <c r="B8" s="15">
         <f>COUNTIF(Findings!$D$6:$D$15,A8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Blocking now</t>
+        </is>
+      </c>
+      <c r="E8" s="13">
+        <f>COUNTIFS('Pre-launch'!$B$6:$B$19,"Now",'Pre-launch'!$G$6:$G$19,"&lt;&gt;Yes")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +2051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
